--- a/epsilon-phi-core/src/Scripts/Case Studies/Private Assets/Commitment Pacing Analysis.xlsx
+++ b/epsilon-phi-core/src/Scripts/Case Studies/Private Assets/Commitment Pacing Analysis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/repo/epsilon-psi/epsilon-phi-core/src/Scripts/Case Studies/Private Assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francisbarker/Repositories/Python/epsilon-phi/epsilon-phi-core/src/Scripts/Case Studies/Private Assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2EB7DC-6FB3-2B46-A520-2986353A5D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09199814-A207-9C4B-9AF4-B81ADA145763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2780" yWindow="1500" windowWidth="28040" windowHeight="17440" xr2:uid="{B27BFF3F-175D-D24A-9917-E1B15F9E6B2E}"/>
+    <workbookView xWindow="23660" yWindow="2160" windowWidth="28040" windowHeight="17440" activeTab="2" xr2:uid="{B27BFF3F-175D-D24A-9917-E1B15F9E6B2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Commitment Pacing" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="20">
   <si>
     <t>Liquid</t>
   </si>
@@ -181,7 +181,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -207,6 +207,7 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -300,61 +301,61 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.3049926757812501E-3</c:v>
+                  <c:v>4.3587913513183597E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.27635315965615E-2</c:v>
+                  <c:v>1.29276779986896E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5118272555327899E-2</c:v>
+                  <c:v>2.5448061593802199E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.9429033788606203E-2</c:v>
+                  <c:v>3.9874388636777003E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.4643202209278603E-2</c:v>
+                  <c:v>5.5163149628896901E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.9787557775812803E-2</c:v>
+                  <c:v>7.0358644219438396E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.3568329092247096E-2</c:v>
+                  <c:v>8.3965737546286404E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.4288124395023806E-2</c:v>
+                  <c:v>9.4428361639111197E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.10099250292793201</c:v>
+                  <c:v>0.10090466188792099</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.103731308282246</c:v>
+                  <c:v>0.103451432078473</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.10387299553014299</c:v>
+                  <c:v>0.103478338686658</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.102916225442211</c:v>
+                  <c:v>0.102470483045261</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.10184368959354299</c:v>
+                  <c:v>0.101385173028133</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.100951466913132</c:v>
+                  <c:v>0.100490011551526</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.100433658178836</c:v>
+                  <c:v>9.9999095200986599E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.10015861750112399</c:v>
+                  <c:v>9.9748276123027904E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.100081950296793</c:v>
+                  <c:v>9.9688417001287694E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.10008658070937</c:v>
+                  <c:v>9.9700916964598499E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.100183879956384</c:v>
+                  <c:v>9.98078414687147E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -404,61 +405,61 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.0718994140624999E-3</c:v>
+                  <c:v>2.11016845703125E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.1384275567630802E-3</c:v>
+                  <c:v>6.2540524059163296E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.1281020647672099E-2</c:v>
+                  <c:v>1.1496115903553501E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.7111430210244302E-2</c:v>
+                  <c:v>1.7406247169617702E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.3203497825282599E-2</c:v>
+                  <c:v>2.3562993855955901E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.9146262614719198E-2</c:v>
+                  <c:v>2.9559889443859001E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.4394447245414898E-2</c:v>
+                  <c:v>3.4765746220456598E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.82914445501078E-2</c:v>
+                  <c:v>3.8582707031830102E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.0554775947362898E-2</c:v>
+                  <c:v>4.0772036895133999E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.13312788473435E-2</c:v>
+                  <c:v>4.1482427743651101E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.1232320493287698E-2</c:v>
+                  <c:v>4.1343237115291802E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.0817800400894999E-2</c:v>
+                  <c:v>4.0910471072208097E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.04076382949239E-2</c:v>
+                  <c:v>4.0495559811140697E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.0080201390122597E-2</c:v>
+                  <c:v>4.0166317897290797E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.98998069222622E-2</c:v>
+                  <c:v>3.9995821713087597E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3.9810732390073003E-2</c:v>
+                  <c:v>3.99153089379456E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3.97942692988872E-2</c:v>
+                  <c:v>3.9904680720428097E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3.9803557340592099E-2</c:v>
+                  <c:v>3.9916541866284599E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3.9844751689357701E-2</c:v>
+                  <c:v>3.99614473565491E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -505,61 +506,61 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.2619628906249998E-4</c:v>
+                  <c:v>7.35260009765625E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.1464420676018999E-3</c:v>
+                  <c:v>2.1740110135137001E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.9898208573999399E-3</c:v>
+                  <c:v>4.04200954927847E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.1404199332067101E-3</c:v>
+                  <c:v>6.2095544547664996E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.4990701503727794E-3</c:v>
+                  <c:v>8.5800310712467395E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.1005915911992801E-2</c:v>
+                  <c:v>1.10962644524745E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3564790273611E-2</c:v>
+                  <c:v>1.3629381058615799E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.5983266850949401E-2</c:v>
+                  <c:v>1.6005746328291701E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.80507812688263E-2</c:v>
+                  <c:v>1.8029198804449701E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.95292629225578E-2</c:v>
+                  <c:v>1.9461495380906801E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.03371524351393E-2</c:v>
+                  <c:v>2.0231776935357E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.0568694198476199E-2</c:v>
+                  <c:v>2.0437791373504301E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.0476519838268301E-2</c:v>
+                  <c:v>2.0331389534443502E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.0283081093618101E-2</c:v>
+                  <c:v>2.0130084648243E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.0129031939056598E-2</c:v>
+                  <c:v>1.99777779366868E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.0020134529521501E-2</c:v>
+                  <c:v>1.9872975610462099E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.9957799952439698E-2</c:v>
+                  <c:v>1.9815142478131698E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.9924135005412201E-2</c:v>
+                  <c:v>1.9784844563434399E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.9923417814953E-2</c:v>
+                  <c:v>1.9787517775463101E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -606,61 +607,61 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.0457763671875001E-3</c:v>
+                  <c:v>5.10665893554687E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.47525583768379E-2</c:v>
+                  <c:v>1.4935871610254999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5152535704737501E-2</c:v>
+                  <c:v>2.54697077343129E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.4748724515775403E-2</c:v>
+                  <c:v>3.51224848307259E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.1089861994061401E-2</c:v>
+                  <c:v>4.1463321457161501E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.3370063308431198E-2</c:v>
+                  <c:v>4.3717670193507099E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.3042275511236398E-2</c:v>
+                  <c:v>4.3269330117080597E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.2083943310568403E-2</c:v>
+                  <c:v>4.2223686459542803E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.1226071281250602E-2</c:v>
+                  <c:v>4.1335993321241597E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.0513199868804098E-2</c:v>
+                  <c:v>4.0619313365287499E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.0002403292654698E-2</c:v>
+                  <c:v>4.0125281128048799E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.9681848118714898E-2</c:v>
+                  <c:v>3.9824703106038299E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.9531601735941703E-2</c:v>
+                  <c:v>3.9687037744256998E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.9485441568345402E-2</c:v>
+                  <c:v>3.9641809251224597E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.9541370026768101E-2</c:v>
+                  <c:v>3.97029555992102E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3.9612455081437903E-2</c:v>
+                  <c:v>3.9775919139922102E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3.9678021743098001E-2</c:v>
+                  <c:v>3.9841834424705097E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3.9708480104330597E-2</c:v>
+                  <c:v>3.9871213207716798E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3.9734384646142401E-2</c:v>
+                  <c:v>3.98984589734575E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -904,20 +905,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1783,64 +1770,64 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>2.39166259765625</c:v>
+                  <c:v>2.4215507507324201</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.3626066122390323</c:v>
+                  <c:v>2.3917393330443093</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.4565441147834512</c:v>
+                  <c:v>2.4844209965808886</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.5368124400756726</c:v>
+                  <c:v>2.5629877286024172</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.6145370771691283</c:v>
+                  <c:v>2.6451958123699213</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.7057977750985813</c:v>
+                  <c:v>2.742030147322605</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.8060776707430941</c:v>
+                  <c:v>2.8477096408935019</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.9117907664140397</c:v>
+                  <c:v>2.9677339943221006</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.0363134235737825</c:v>
+                  <c:v>3.109039819314261</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.1847868940526234</c:v>
+                  <c:v>3.2743990088040213</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.36492265055732</c:v>
+                  <c:v>3.4735163573107051</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.5709446012019637</c:v>
+                  <c:v>3.699915863528358</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.798056623803356</c:v>
+                  <c:v>3.9493431251503268</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.0405830913118903</c:v>
+                  <c:v>4.2165915874016484</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>4.2989916316932852</c:v>
+                  <c:v>4.5030801536418199</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.5657609758473194</c:v>
+                  <c:v>4.7992091149516467</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.8469189126818035</c:v>
+                  <c:v>5.1126738701637784</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.1428121516265124</c:v>
+                  <c:v>5.4439929712345556</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>5.4582609196768361</c:v>
+                  <c:v>5.7985588229329785</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5.7898476649691251</c:v>
+                  <c:v>6.1722653384542161</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1887,64 +1874,64 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0.94177246093750011</c:v>
+                  <c:v>0.95916748046875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.93033099468797431</c:v>
+                  <c:v>0.94735928591224183</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.96732105885182229</c:v>
+                  <c:v>0.98407015710630852</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.99892856833909993</c:v>
+                  <c:v>1.0151901550576048</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0295344417690353</c:v>
+                  <c:v>1.0477524792449429</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0654704522080161</c:v>
+                  <c:v>1.0861082085441698</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.1049579803385463</c:v>
+                  <c:v>1.1279674731311096</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.1465849566356676</c:v>
+                  <c:v>1.1755086847444445</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.1956186327866138</c:v>
+                  <c:v>1.2314794101534801</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.2540834956037255</c:v>
+                  <c:v>1.2969775861084032</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.3250161158121589</c:v>
+                  <c:v>1.3758472465633855</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.4061420236454332</c:v>
+                  <c:v>1.4655232708599959</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.4955726350717311</c:v>
+                  <c:v>1.56432050565584</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.591073040677363</c:v>
+                  <c:v>1.6701766534649318</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.6928273797888833</c:v>
+                  <c:v>1.7836537367680907</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.7978739787501374</c:v>
+                  <c:v>1.9009493456366904</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.9085864188510966</c:v>
+                  <c:v>2.0251115996723059</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.0251012249482478</c:v>
+                  <c:v>2.1563458954264254</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.1493164729006913</c:v>
+                  <c:v>2.2967881448944452</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.2798864226227789</c:v>
+                  <c:v>2.4448119419669805</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1988,64 +1975,64 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>0.40344238281249994</c:v>
+                  <c:v>0.408477783203125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.39854101587086904</c:v>
+                  <c:v>0.40344906274054587</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.41438705113483759</c:v>
+                  <c:v>0.41908301154527322</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.42792727392880425</c:v>
+                  <c:v>0.43233599190092392</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.44103840959775259</c:v>
+                  <c:v>0.44620321141245811</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.45643290272812603</c:v>
+                  <c:v>0.46253765101379929</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.47334881724159367</c:v>
+                  <c:v>0.48036413069869233</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.49118124195474799</c:v>
+                  <c:v>0.5006103641522236</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.51218659512116116</c:v>
+                  <c:v>0.52444644940834639</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.53723213907586675</c:v>
+                  <c:v>0.55233996150368991</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.56761869899665385</c:v>
+                  <c:v>0.58592794766945322</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.60237192328556788</c:v>
+                  <c:v>0.62411800765068548</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.64068276849151917</c:v>
+                  <c:v>0.66619249023873428</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.68159383012815089</c:v>
+                  <c:v>0.7112731309776682</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.72518399095298225</c:v>
+                  <c:v>0.75959927669872385</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.77018451066353899</c:v>
+                  <c:v>0.80955160646984092</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.81761219887269909</c:v>
+                  <c:v>0.86242821385980939</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.86752554095320256</c:v>
+                  <c:v>0.91831657048306392</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.92073764652453449</c:v>
+                  <c:v>0.9781262907862599</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.97667201902375678</c:v>
+                  <c:v>1.0411647420689796</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2089,64 +2076,64 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>1.441650390625</c:v>
+                  <c:v>1.45904541015625</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4241359750181433</c:v>
+                  <c:v>1.4410832790157266</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.4807597803033079</c:v>
+                  <c:v>1.4969263191617119</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.5291440560058027</c:v>
+                  <c:v>1.5442647570252652</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.5759950430709404</c:v>
+                  <c:v>1.5937972011676971</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.6310053195821994</c:v>
+                  <c:v>1.6521423305916882</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.691452203214288</c:v>
+                  <c:v>1.7158168911994383</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.7551741202679498</c:v>
+                  <c:v>1.7881345917159366</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.8302340963331052</c:v>
+                  <c:v>1.8732749156677657</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.9197311838081654</c:v>
+                  <c:v>1.9729079984677935</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.0283137171408416</c:v>
+                  <c:v>2.0928812236142371</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.1524999739795936</c:v>
+                  <c:v>2.2292926369652055</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.2893989397533558</c:v>
+                  <c:v>2.3795788538150084</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.4355894504730595</c:v>
+                  <c:v>2.5406027935780591</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.5913533837079337</c:v>
+                  <c:v>2.7132193813198349</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.7521570562591213</c:v>
+                  <c:v>2.8916445502669479</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.921633908831037</c:v>
+                  <c:v>3.0805149723300329</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3.0999929315150752</c:v>
+                  <c:v>3.2801430881430922</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3.290139668821408</c:v>
+                  <c:v>3.493777957601127</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3.4900140831075848</c:v>
+                  <c:v>3.7189455598295047</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2267,64 +2254,64 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>5.17852783203125</c:v>
+                  <c:v>5.2482414245605442</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.1156145978160188</c:v>
+                  <c:v>5.183630960712823</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.3190120050734189</c:v>
+                  <c:v>5.3845004843941817</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.4928123383493794</c:v>
+                  <c:v>5.5547786325862099</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.6611049716068562</c:v>
+                  <c:v>5.7329487041950182</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.858706449616923</c:v>
+                  <c:v>5.9428183374722616</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.0758366715375223</c:v>
+                  <c:v>6.1718581359227409</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.3047310852724054</c:v>
+                  <c:v>6.4319876349347043</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.5743527478146628</c:v>
+                  <c:v>6.7382405945438517</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.895833712540381</c:v>
+                  <c:v>7.0966245548839071</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.2858711825069751</c:v>
+                  <c:v>7.5281727751577794</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.7319585221125591</c:v>
+                  <c:v>8.0188497790042437</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.2237109671199615</c:v>
+                  <c:v>8.5594349748599079</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8.7488394125904652</c:v>
+                  <c:v>9.1386441654223063</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9.3083563861430854</c:v>
+                  <c:v>9.7595525484284682</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.8859765215201172</c:v>
+                  <c:v>10.401354617325124</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>10.494751439236635</c:v>
+                  <c:v>11.080728656025924</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>11.135431849043039</c:v>
+                  <c:v>11.798798525287134</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>11.81845470792347</c:v>
+                  <c:v>12.567251216214808</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>12.536420189723247</c:v>
+                  <c:v>13.37718758231968</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2449,20 +2436,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -7517,7 +7490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28BF1DFD-D473-E647-A67C-FA89D99FB3BA}">
-  <dimension ref="A1:P87"/>
+  <dimension ref="A1:W87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -7527,7 +7500,7 @@
     <col min="10" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C1" s="2">
         <v>0.6</v>
       </c>
@@ -7536,7 +7509,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -7577,12 +7550,27 @@
       <c r="P2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="S2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>0</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="11">
         <v>1</v>
       </c>
       <c r="C3" s="4">
@@ -7624,13 +7612,31 @@
       <c r="P3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <v>1</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1">
+        <v>0</v>
+      </c>
+      <c r="V3" s="1">
+        <v>0</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="4">
-        <v>0.987851135253906</v>
+      <c r="B4" s="11">
+        <v>0.98768912124633701</v>
       </c>
       <c r="C4" s="4">
         <v>0.59125281738281221</v>
@@ -7639,16 +7645,16 @@
         <v>0.39416854492187481</v>
       </c>
       <c r="E4" s="4">
-        <v>4.3049926757812501E-3</v>
+        <v>4.3587913513183597E-3</v>
       </c>
       <c r="F4" s="4">
-        <v>2.0718994140624999E-3</v>
+        <v>2.11016845703125E-3</v>
       </c>
       <c r="G4" s="4">
-        <v>7.2619628906249998E-4</v>
+        <v>7.35260009765625E-4</v>
       </c>
       <c r="H4" s="4">
-        <v>5.0457763671875001E-3</v>
+        <v>5.10665893554687E-3</v>
       </c>
       <c r="I4" s="4">
         <v>0.2</v>
@@ -7671,13 +7677,31 @@
       <c r="P4" s="1">
         <v>5.0457763671875001E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R4" s="1">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0.98768912124633701</v>
+      </c>
+      <c r="T4" s="1">
+        <v>4.3587913513183597E-3</v>
+      </c>
+      <c r="U4" s="1">
+        <v>2.11016845703125E-3</v>
+      </c>
+      <c r="V4" s="1">
+        <v>7.35260009765625E-4</v>
+      </c>
+      <c r="W4" s="1">
+        <v>5.10665893554687E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>2</v>
       </c>
-      <c r="B5" s="4">
-        <v>0.96419904040223503</v>
+      <c r="B5" s="11">
+        <v>0.96370838697162498</v>
       </c>
       <c r="C5" s="4">
         <v>0.57438234628160156</v>
@@ -7686,16 +7710,16 @@
         <v>0.38292156418773443</v>
       </c>
       <c r="E5" s="4">
-        <v>1.27635315965615E-2</v>
+        <v>1.29276779986896E-2</v>
       </c>
       <c r="F5" s="4">
-        <v>6.1384275567630802E-3</v>
+        <v>6.2540524059163296E-3</v>
       </c>
       <c r="G5" s="4">
-        <v>2.1464420676018999E-3</v>
+        <v>2.1740110135137001E-3</v>
       </c>
       <c r="H5" s="4">
-        <v>1.47525583768379E-2</v>
+        <v>1.4935871610254999E-2</v>
       </c>
       <c r="I5" s="4">
         <v>0.2</v>
@@ -7718,13 +7742,31 @@
       <c r="P5" s="1">
         <v>1.47525583768379E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R5" s="1">
+        <v>2</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0.96370838697162498</v>
+      </c>
+      <c r="T5" s="1">
+        <v>1.29276779986896E-2</v>
+      </c>
+      <c r="U5" s="1">
+        <v>6.2540524059163296E-3</v>
+      </c>
+      <c r="V5" s="1">
+        <v>2.1740110135137001E-3</v>
+      </c>
+      <c r="W5" s="1">
+        <v>1.4935871610254999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>3</v>
       </c>
-      <c r="B6" s="4">
-        <v>0.93445835023486201</v>
+      <c r="B6" s="11">
+        <v>0.93354410521905196</v>
       </c>
       <c r="C6" s="4">
         <v>0.55357404748191119</v>
@@ -7733,16 +7775,16 @@
         <v>0.36904936498794083</v>
       </c>
       <c r="E6" s="4">
-        <v>2.5118272555327899E-2</v>
+        <v>2.5448061593802199E-2</v>
       </c>
       <c r="F6" s="4">
-        <v>1.1281020647672099E-2</v>
+        <v>1.1496115903553501E-2</v>
       </c>
       <c r="G6" s="4">
-        <v>3.9898208573999399E-3</v>
+        <v>4.04200954927847E-3</v>
       </c>
       <c r="H6" s="4">
-        <v>2.5152535704737501E-2</v>
+        <v>2.54697077343129E-2</v>
       </c>
       <c r="I6" s="4">
         <v>0.2</v>
@@ -7765,13 +7807,31 @@
       <c r="P6" s="1">
         <v>2.5152535704737501E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R6" s="1">
+        <v>3</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0.93354410521905196</v>
+      </c>
+      <c r="T6" s="1">
+        <v>2.5448061593802199E-2</v>
+      </c>
+      <c r="U6" s="1">
+        <v>1.1496115903553501E-2</v>
+      </c>
+      <c r="V6" s="1">
+        <v>4.04200954927847E-3</v>
+      </c>
+      <c r="W6" s="1">
+        <v>2.54697077343129E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>4</v>
       </c>
-      <c r="B7" s="4">
-        <v>0.90257039155216701</v>
+      <c r="B7" s="11">
+        <v>0.90138732490811202</v>
       </c>
       <c r="C7" s="4">
         <v>0.53187852968983496</v>
@@ -7780,16 +7840,16 @@
         <v>0.35458568645989003</v>
       </c>
       <c r="E7" s="4">
-        <v>3.9429033788606203E-2</v>
+        <v>3.9874388636777003E-2</v>
       </c>
       <c r="F7" s="4">
-        <v>1.7111430210244302E-2</v>
+        <v>1.7406247169617702E-2</v>
       </c>
       <c r="G7" s="4">
-        <v>6.1404199332067101E-3</v>
+        <v>6.2095544547664996E-3</v>
       </c>
       <c r="H7" s="4">
-        <v>3.4748724515775403E-2</v>
+        <v>3.51224848307259E-2</v>
       </c>
       <c r="I7" s="4">
         <v>0.2</v>
@@ -7812,13 +7872,31 @@
       <c r="P7" s="1">
         <v>3.4748724515775403E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R7" s="1">
+        <v>4</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0.90138732490811202</v>
+      </c>
+      <c r="T7" s="1">
+        <v>3.9874388636777003E-2</v>
+      </c>
+      <c r="U7" s="1">
+        <v>1.7406247169617702E-2</v>
+      </c>
+      <c r="V7" s="1">
+        <v>6.2095544547664996E-3</v>
+      </c>
+      <c r="W7" s="1">
+        <v>3.51224848307259E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>5</v>
       </c>
-      <c r="B8" s="4">
-        <v>0.87256436782100399</v>
+      <c r="B8" s="11">
+        <v>0.87123050398673796</v>
       </c>
       <c r="C8" s="4">
         <v>0.51224351174471938</v>
@@ -7827,16 +7905,16 @@
         <v>0.34149567449647966</v>
       </c>
       <c r="E8" s="4">
-        <v>5.4643202209278603E-2</v>
+        <v>5.5163149628896901E-2</v>
       </c>
       <c r="F8" s="4">
-        <v>2.3203497825282599E-2</v>
+        <v>2.3562993855955901E-2</v>
       </c>
       <c r="G8" s="4">
-        <v>8.4990701503727794E-3</v>
+        <v>8.5800310712467395E-3</v>
       </c>
       <c r="H8" s="4">
-        <v>4.1089861994061401E-2</v>
+        <v>4.1463321457161501E-2</v>
       </c>
       <c r="I8" s="4">
         <v>0.2</v>
@@ -7859,13 +7937,31 @@
       <c r="P8" s="1">
         <v>4.1089861994061401E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R8" s="1">
+        <v>5</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0.87123050398673796</v>
+      </c>
+      <c r="T8" s="1">
+        <v>5.5163149628896901E-2</v>
+      </c>
+      <c r="U8" s="1">
+        <v>2.3562993855955901E-2</v>
+      </c>
+      <c r="V8" s="1">
+        <v>8.5800310712467395E-3</v>
+      </c>
+      <c r="W8" s="1">
+        <v>4.1463321457161501E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>6</v>
       </c>
-      <c r="B9" s="4">
-        <v>0.84669020038904297</v>
+      <c r="B9" s="11">
+        <v>0.84526753169072</v>
       </c>
       <c r="C9" s="4">
         <v>0.49611303538544937</v>
@@ -7874,16 +7970,16 @@
         <v>0.33074202359029958</v>
       </c>
       <c r="E9" s="4">
-        <v>6.9787557775812803E-2</v>
+        <v>7.0358644219438396E-2</v>
       </c>
       <c r="F9" s="4">
-        <v>2.9146262614719198E-2</v>
+        <v>2.9559889443859001E-2</v>
       </c>
       <c r="G9" s="4">
-        <v>1.1005915911992801E-2</v>
+        <v>1.10962644524745E-2</v>
       </c>
       <c r="H9" s="4">
-        <v>4.3370063308431198E-2</v>
+        <v>4.3717670193507099E-2</v>
       </c>
       <c r="I9" s="4">
         <v>0.2</v>
@@ -7906,13 +8002,31 @@
       <c r="P9" s="1">
         <v>4.3370063308431198E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R9" s="1">
+        <v>6</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0.84526753169072</v>
+      </c>
+      <c r="T9" s="1">
+        <v>7.0358644219438396E-2</v>
+      </c>
+      <c r="U9" s="1">
+        <v>2.9559889443859001E-2</v>
+      </c>
+      <c r="V9" s="1">
+        <v>1.10962644524745E-2</v>
+      </c>
+      <c r="W9" s="1">
+        <v>4.3717670193507099E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>7</v>
       </c>
-      <c r="B10" s="4">
-        <v>0.82543015787748997</v>
+      <c r="B10" s="11">
+        <v>0.82436980505755997</v>
       </c>
       <c r="C10" s="4">
         <v>0.48359741273882095</v>
@@ -7921,16 +8035,16 @@
         <v>0.32239827515921404</v>
       </c>
       <c r="E10" s="4">
-        <v>8.3568329092247096E-2</v>
+        <v>8.3965737546286404E-2</v>
       </c>
       <c r="F10" s="4">
-        <v>3.4394447245414898E-2</v>
+        <v>3.4765746220456598E-2</v>
       </c>
       <c r="G10" s="4">
-        <v>1.3564790273611E-2</v>
+        <v>1.3629381058615799E-2</v>
       </c>
       <c r="H10" s="4">
-        <v>4.3042275511236398E-2</v>
+        <v>4.3269330117080597E-2</v>
       </c>
       <c r="I10" s="4">
         <v>0.2</v>
@@ -7953,13 +8067,31 @@
       <c r="P10" s="1">
         <v>4.3042275511236398E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R10" s="1">
+        <v>7</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0.82436980505755997</v>
+      </c>
+      <c r="T10" s="1">
+        <v>8.3965737546286404E-2</v>
+      </c>
+      <c r="U10" s="1">
+        <v>3.4765746220456598E-2</v>
+      </c>
+      <c r="V10" s="1">
+        <v>1.3629381058615799E-2</v>
+      </c>
+      <c r="W10" s="1">
+        <v>4.3269330117080597E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>8</v>
       </c>
-      <c r="B11" s="4">
-        <v>0.80935322089335004</v>
+      <c r="B11" s="11">
+        <v>0.80875949854122398</v>
       </c>
       <c r="C11" s="4">
         <v>0.47488763783579158</v>
@@ -7968,16 +8100,16 @@
         <v>0.31659175855719446</v>
       </c>
       <c r="E11" s="4">
-        <v>9.4288124395023806E-2</v>
+        <v>9.4428361639111197E-2</v>
       </c>
       <c r="F11" s="4">
-        <v>3.82914445501078E-2</v>
+        <v>3.8582707031830102E-2</v>
       </c>
       <c r="G11" s="4">
-        <v>1.5983266850949401E-2</v>
+        <v>1.6005746328291701E-2</v>
       </c>
       <c r="H11" s="4">
-        <v>4.2083943310568403E-2</v>
+        <v>4.2223686459542803E-2</v>
       </c>
       <c r="I11" s="4">
         <v>0.2</v>
@@ -8000,13 +8132,31 @@
       <c r="P11" s="1">
         <v>4.2083943310568403E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R11" s="1">
+        <v>8</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0.80875949854122398</v>
+      </c>
+      <c r="T11" s="1">
+        <v>9.4428361639111197E-2</v>
+      </c>
+      <c r="U11" s="1">
+        <v>3.8582707031830102E-2</v>
+      </c>
+      <c r="V11" s="1">
+        <v>1.6005746328291701E-2</v>
+      </c>
+      <c r="W11" s="1">
+        <v>4.2223686459542803E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>9</v>
       </c>
-      <c r="B12" s="4">
-        <v>0.79917586857462697</v>
+      <c r="B12" s="11">
+        <v>0.79895810909125298</v>
       </c>
       <c r="C12" s="4">
         <v>0.47031766420166099</v>
@@ -8015,16 +8165,16 @@
         <v>0.31354510946777403</v>
       </c>
       <c r="E12" s="4">
-        <v>0.10099250292793201</v>
+        <v>0.10090466188792099</v>
       </c>
       <c r="F12" s="4">
-        <v>4.0554775947362898E-2</v>
+        <v>4.0772036895133999E-2</v>
       </c>
       <c r="G12" s="4">
-        <v>1.80507812688263E-2</v>
+        <v>1.8029198804449701E-2</v>
       </c>
       <c r="H12" s="4">
-        <v>4.1226071281250602E-2</v>
+        <v>4.1335993321241597E-2</v>
       </c>
       <c r="I12" s="4">
         <v>0.2</v>
@@ -8047,13 +8197,31 @@
       <c r="P12" s="1">
         <v>4.1226071281250602E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R12" s="1">
+        <v>9</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0.79895810909125298</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0.10090466188792099</v>
+      </c>
+      <c r="U12" s="1">
+        <v>4.0772036895133999E-2</v>
+      </c>
+      <c r="V12" s="1">
+        <v>1.8029198804449701E-2</v>
+      </c>
+      <c r="W12" s="1">
+        <v>4.1335993321241597E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>10</v>
       </c>
-      <c r="B13" s="4">
-        <v>0.79489495007904698</v>
+      <c r="B13" s="11">
+        <v>0.79498533143168004</v>
       </c>
       <c r="C13" s="4">
         <v>0.46974303500079773</v>
@@ -8062,16 +8230,16 @@
         <v>0.31316202333386522</v>
       </c>
       <c r="E13" s="4">
-        <v>0.103731308282246</v>
+        <v>0.103451432078473</v>
       </c>
       <c r="F13" s="4">
-        <v>4.13312788473435E-2</v>
+        <v>4.1482427743651101E-2</v>
       </c>
       <c r="G13" s="4">
-        <v>1.95292629225578E-2</v>
+        <v>1.9461495380906801E-2</v>
       </c>
       <c r="H13" s="4">
-        <v>4.0513199868804098E-2</v>
+        <v>4.0619313365287499E-2</v>
       </c>
       <c r="I13" s="4">
         <v>0.2</v>
@@ -8094,13 +8262,31 @@
       <c r="P13" s="1">
         <v>4.0513199868804098E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R13" s="1">
+        <v>10</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0.79498533143168004</v>
+      </c>
+      <c r="T13" s="1">
+        <v>0.103451432078473</v>
+      </c>
+      <c r="U13" s="1">
+        <v>4.1482427743651101E-2</v>
+      </c>
+      <c r="V13" s="1">
+        <v>1.9461495380906801E-2</v>
+      </c>
+      <c r="W13" s="1">
+        <v>4.0619313365287499E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>11</v>
       </c>
-      <c r="B14" s="4">
-        <v>0.79455512824877395</v>
+      <c r="B14" s="11">
+        <v>0.79482136613464405</v>
       </c>
       <c r="C14" s="4">
         <v>0.47168570215327077</v>
@@ -8109,16 +8295,16 @@
         <v>0.31445713476884718</v>
       </c>
       <c r="E14" s="4">
-        <v>0.10387299553014299</v>
+        <v>0.103478338686658</v>
       </c>
       <c r="F14" s="4">
-        <v>4.1232320493287698E-2</v>
+        <v>4.1343237115291802E-2</v>
       </c>
       <c r="G14" s="4">
-        <v>2.03371524351393E-2</v>
+        <v>2.0231776935357E-2</v>
       </c>
       <c r="H14" s="4">
-        <v>4.0002403292654698E-2</v>
+        <v>4.0125281128048799E-2</v>
       </c>
       <c r="I14" s="4">
         <v>0.2</v>
@@ -8141,13 +8327,31 @@
       <c r="P14" s="1">
         <v>4.0002403292654698E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R14" s="1">
+        <v>11</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0.79482136613464405</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0.103478338686658</v>
+      </c>
+      <c r="U14" s="1">
+        <v>4.1343237115291802E-2</v>
+      </c>
+      <c r="V14" s="1">
+        <v>2.0231776935357E-2</v>
+      </c>
+      <c r="W14" s="1">
+        <v>4.0125281128048799E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>12</v>
       </c>
-      <c r="B15" s="4">
-        <v>0.79601543183970203</v>
+      <c r="B15" s="11">
+        <v>0.796356551402987</v>
       </c>
       <c r="C15" s="4">
         <v>0.4745232193463178</v>
@@ -8156,16 +8360,16 @@
         <v>0.31634881289754524</v>
       </c>
       <c r="E15" s="4">
-        <v>0.102916225442211</v>
+        <v>0.102470483045261</v>
       </c>
       <c r="F15" s="4">
-        <v>4.0817800400894999E-2</v>
+        <v>4.0910471072208097E-2</v>
       </c>
       <c r="G15" s="4">
-        <v>2.0568694198476199E-2</v>
+        <v>2.0437791373504301E-2</v>
       </c>
       <c r="H15" s="4">
-        <v>3.9681848118714898E-2</v>
+        <v>3.9824703106038299E-2</v>
       </c>
       <c r="I15" s="4">
         <v>0.2</v>
@@ -8188,13 +8392,31 @@
       <c r="P15" s="1">
         <v>3.9681848118714898E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R15" s="1">
+        <v>12</v>
+      </c>
+      <c r="S15" s="1">
+        <v>0.796356551402987</v>
+      </c>
+      <c r="T15" s="1">
+        <v>0.102470483045261</v>
+      </c>
+      <c r="U15" s="1">
+        <v>4.0910471072208097E-2</v>
+      </c>
+      <c r="V15" s="1">
+        <v>2.0437791373504301E-2</v>
+      </c>
+      <c r="W15" s="1">
+        <v>3.9824703106038299E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>13</v>
       </c>
-      <c r="B16" s="4">
-        <v>0.79774055053732196</v>
+      <c r="B16" s="11">
+        <v>0.79810083988202396</v>
       </c>
       <c r="C16" s="4">
         <v>0.47709586022220957</v>
@@ -8203,16 +8425,16 @@
         <v>0.3180639068148064</v>
       </c>
       <c r="E16" s="4">
-        <v>0.10184368959354299</v>
+        <v>0.101385173028133</v>
       </c>
       <c r="F16" s="4">
-        <v>4.04076382949239E-2</v>
+        <v>4.0495559811140697E-2</v>
       </c>
       <c r="G16" s="4">
-        <v>2.0476519838268301E-2</v>
+        <v>2.0331389534443502E-2</v>
       </c>
       <c r="H16" s="4">
-        <v>3.9531601735941703E-2</v>
+        <v>3.9687037744256998E-2</v>
       </c>
       <c r="I16" s="4">
         <v>0.2</v>
@@ -8235,13 +8457,31 @@
       <c r="P16" s="1">
         <v>3.9531601735941703E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R16" s="1">
+        <v>13</v>
+      </c>
+      <c r="S16" s="1">
+        <v>0.79810083988202396</v>
+      </c>
+      <c r="T16" s="1">
+        <v>0.101385173028133</v>
+      </c>
+      <c r="U16" s="1">
+        <v>4.0495559811140697E-2</v>
+      </c>
+      <c r="V16" s="1">
+        <v>2.0331389534443502E-2</v>
+      </c>
+      <c r="W16" s="1">
+        <v>3.9687037744256998E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>14</v>
       </c>
-      <c r="B17" s="4">
-        <v>0.79919980903478105</v>
+      <c r="B17" s="11">
+        <v>0.79957177665171497</v>
       </c>
       <c r="C17" s="4">
         <v>0.47900840229623637</v>
@@ -8250,16 +8490,16 @@
         <v>0.3193389348641576</v>
       </c>
       <c r="E17" s="4">
-        <v>0.100951466913132</v>
+        <v>0.100490011551526</v>
       </c>
       <c r="F17" s="4">
-        <v>4.0080201390122597E-2</v>
+        <v>4.0166317897290797E-2</v>
       </c>
       <c r="G17" s="4">
-        <v>2.0283081093618101E-2</v>
+        <v>2.0130084648243E-2</v>
       </c>
       <c r="H17" s="4">
-        <v>3.9485441568345402E-2</v>
+        <v>3.9641809251224597E-2</v>
       </c>
       <c r="I17" s="4">
         <v>0.2</v>
@@ -8282,13 +8522,31 @@
       <c r="P17" s="1">
         <v>3.9485441568345402E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R17" s="1">
+        <v>14</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0.79957177665171497</v>
+      </c>
+      <c r="T17" s="1">
+        <v>0.100490011551526</v>
+      </c>
+      <c r="U17" s="1">
+        <v>4.0166317897290797E-2</v>
+      </c>
+      <c r="V17" s="1">
+        <v>2.0130084648243E-2</v>
+      </c>
+      <c r="W17" s="1">
+        <v>3.9641809251224597E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>15</v>
       </c>
-      <c r="B18" s="4">
-        <v>0.79999613293307603</v>
+      <c r="B18" s="11">
+        <v>0.80032434955002796</v>
       </c>
       <c r="C18" s="4">
         <v>0.48006717023100243</v>
@@ -8297,16 +8555,16 @@
         <v>0.32004478015400162</v>
       </c>
       <c r="E18" s="4">
-        <v>0.100433658178836</v>
+        <v>9.9999095200986599E-2</v>
       </c>
       <c r="F18" s="4">
-        <v>3.98998069222622E-2</v>
+        <v>3.9995821713087597E-2</v>
       </c>
       <c r="G18" s="4">
-        <v>2.0129031939056598E-2</v>
+        <v>1.99777779366868E-2</v>
       </c>
       <c r="H18" s="4">
-        <v>3.9541370026768101E-2</v>
+        <v>3.97029555992102E-2</v>
       </c>
       <c r="I18" s="4">
         <v>0.2</v>
@@ -8329,13 +8587,31 @@
       <c r="P18" s="1">
         <v>3.9541370026768101E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R18" s="1">
+        <v>15</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0.80032434955002796</v>
+      </c>
+      <c r="T18" s="1">
+        <v>9.9999095200986599E-2</v>
+      </c>
+      <c r="U18" s="1">
+        <v>3.9995821713087597E-2</v>
+      </c>
+      <c r="V18" s="1">
+        <v>1.99777779366868E-2</v>
+      </c>
+      <c r="W18" s="1">
+        <v>3.97029555992102E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>16</v>
       </c>
-      <c r="B19" s="4">
-        <v>0.80039806049784301</v>
+      <c r="B19" s="11">
+        <v>0.80068752018864198</v>
       </c>
       <c r="C19" s="4">
         <v>0.48054298340907481</v>
@@ -8344,16 +8620,16 @@
         <v>0.32036198893938322</v>
       </c>
       <c r="E19" s="4">
-        <v>0.10015861750112399</v>
+        <v>9.9748276123027904E-2</v>
       </c>
       <c r="F19" s="4">
-        <v>3.9810732390073003E-2</v>
+        <v>3.99153089379456E-2</v>
       </c>
       <c r="G19" s="4">
-        <v>2.0020134529521501E-2</v>
+        <v>1.9872975610462099E-2</v>
       </c>
       <c r="H19" s="4">
-        <v>3.9612455081437903E-2</v>
+        <v>3.9775919139922102E-2</v>
       </c>
       <c r="I19" s="4">
         <v>0.2</v>
@@ -8376,13 +8652,31 @@
       <c r="P19" s="1">
         <v>3.9612455081437903E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R19" s="1">
+        <v>16</v>
+      </c>
+      <c r="S19" s="1">
+        <v>0.80068752018864198</v>
+      </c>
+      <c r="T19" s="1">
+        <v>9.9748276123027904E-2</v>
+      </c>
+      <c r="U19" s="1">
+        <v>3.99153089379456E-2</v>
+      </c>
+      <c r="V19" s="1">
+        <v>1.9872975610462099E-2</v>
+      </c>
+      <c r="W19" s="1">
+        <v>3.9775919139922102E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>17</v>
       </c>
-      <c r="B20" s="4">
-        <v>0.80048795870878098</v>
+      <c r="B20" s="11">
+        <v>0.80074992537544698</v>
       </c>
       <c r="C20" s="4">
         <v>0.48061316101592333</v>
@@ -8391,16 +8685,16 @@
         <v>0.32040877401061563</v>
       </c>
       <c r="E20" s="4">
-        <v>0.100081950296793</v>
+        <v>9.9688417001287694E-2</v>
       </c>
       <c r="F20" s="4">
-        <v>3.97942692988872E-2</v>
+        <v>3.9904680720428097E-2</v>
       </c>
       <c r="G20" s="4">
-        <v>1.9957799952439698E-2</v>
+        <v>1.9815142478131698E-2</v>
       </c>
       <c r="H20" s="4">
-        <v>3.9678021743098001E-2</v>
+        <v>3.9841834424705097E-2</v>
       </c>
       <c r="I20" s="4">
         <v>0.2</v>
@@ -8423,13 +8717,31 @@
       <c r="P20" s="1">
         <v>3.9678021743098001E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R20" s="1">
+        <v>17</v>
+      </c>
+      <c r="S20" s="1">
+        <v>0.80074992537544698</v>
+      </c>
+      <c r="T20" s="1">
+        <v>9.9688417001287694E-2</v>
+      </c>
+      <c r="U20" s="1">
+        <v>3.9904680720428097E-2</v>
+      </c>
+      <c r="V20" s="1">
+        <v>1.9815142478131698E-2</v>
+      </c>
+      <c r="W20" s="1">
+        <v>3.9841834424705097E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>18</v>
       </c>
-      <c r="B21" s="4">
-        <v>0.80047724684029398</v>
+      <c r="B21" s="11">
+        <v>0.80072648339796504</v>
       </c>
       <c r="C21" s="4">
         <v>0.48051878740322695</v>
@@ -8438,16 +8750,16 @@
         <v>0.32034585826881801</v>
       </c>
       <c r="E21" s="4">
-        <v>0.10008658070937</v>
+        <v>9.9700916964598499E-2</v>
       </c>
       <c r="F21" s="4">
-        <v>3.9803557340592099E-2</v>
+        <v>3.9916541866284599E-2</v>
       </c>
       <c r="G21" s="4">
-        <v>1.9924135005412201E-2</v>
+        <v>1.9784844563434399E-2</v>
       </c>
       <c r="H21" s="4">
-        <v>3.9708480104330597E-2</v>
+        <v>3.9871213207716798E-2</v>
       </c>
       <c r="I21" s="4">
         <v>0.2</v>
@@ -8470,13 +8782,31 @@
       <c r="P21" s="1">
         <v>3.9708480104330597E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="R21" s="1">
+        <v>18</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0.80072648339796504</v>
+      </c>
+      <c r="T21" s="1">
+        <v>9.9700916964598499E-2</v>
+      </c>
+      <c r="U21" s="1">
+        <v>3.9916541866284599E-2</v>
+      </c>
+      <c r="V21" s="1">
+        <v>1.9784844563434399E-2</v>
+      </c>
+      <c r="W21" s="1">
+        <v>3.9871213207716798E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>19</v>
       </c>
-      <c r="B22" s="4">
-        <v>0.80031356589316105</v>
+      <c r="B22" s="11">
+        <v>0.80054473442581497</v>
       </c>
       <c r="C22" s="4">
         <v>0.48030734164977773</v>
@@ -8485,16 +8815,16 @@
         <v>0.32020489443318523</v>
       </c>
       <c r="E22" s="4">
-        <v>0.100183879956384</v>
+        <v>9.98078414687147E-2</v>
       </c>
       <c r="F22" s="4">
-        <v>3.9844751689357701E-2</v>
+        <v>3.99614473565491E-2</v>
       </c>
       <c r="G22" s="4">
-        <v>1.9923417814953E-2</v>
+        <v>1.9787517775463101E-2</v>
       </c>
       <c r="H22" s="4">
-        <v>3.9734384646142401E-2</v>
+        <v>3.98984589734575E-2</v>
       </c>
       <c r="I22" s="4">
         <v>0.2</v>
@@ -8516,6 +8846,24 @@
       </c>
       <c r="P22" s="1">
         <v>3.9734384646142401E-2</v>
+      </c>
+      <c r="R22" s="1">
+        <v>19</v>
+      </c>
+      <c r="S22" s="1">
+        <v>0.80054473442581497</v>
+      </c>
+      <c r="T22" s="1">
+        <v>9.98078414687147E-2</v>
+      </c>
+      <c r="U22" s="1">
+        <v>3.99614473565491E-2</v>
+      </c>
+      <c r="V22" s="1">
+        <v>1.9787517775463101E-2</v>
+      </c>
+      <c r="W22" s="1">
+        <v>3.98984589734575E-2</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -9325,13 +9673,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E78B60E-C37E-4C47-9128-A3AA854415E4}">
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:X50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="68" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="68" x14ac:dyDescent="0.2">
       <c r="B1" s="8" t="s">
         <v>14</v>
       </c>
@@ -9351,7 +9699,7 @@
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -9362,8 +9710,20 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="U2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
@@ -9400,26 +9760,41 @@
       <c r="Q3" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="T3" s="1">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V3" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W3" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X3" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>0</v>
       </c>
-      <c r="B4" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C4" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D4" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B4" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F4" s="3">
         <f>SUM(B4:E4)</f>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -9439,1106 +9814,1619 @@
       </c>
       <c r="M4" s="9">
         <f>$J4*B4</f>
-        <v>2.39166259765625</v>
+        <v>2.4215507507324201</v>
       </c>
       <c r="N4" s="9">
         <f t="shared" ref="N4:Q4" si="0">$J4*C4</f>
-        <v>0.94177246093750011</v>
+        <v>0.95916748046875</v>
       </c>
       <c r="O4" s="9">
         <f t="shared" si="0"/>
-        <v>0.40344238281249994</v>
+        <v>0.408477783203125</v>
       </c>
       <c r="P4" s="9">
         <f t="shared" si="0"/>
-        <v>1.441650390625</v>
+        <v>1.45904541015625</v>
       </c>
       <c r="Q4" s="9">
         <f t="shared" si="0"/>
-        <v>5.17852783203125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+        <v>5.2482414245605442</v>
+      </c>
+      <c r="T4" s="1">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V4" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W4" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X4" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C5" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D5" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B5" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F5" s="3">
         <f t="shared" ref="F5:F23" si="1">SUM(B5:E5)</f>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>49.3925567626953</v>
+        <v>49.384456062316801</v>
       </c>
       <c r="I5" s="1">
-        <v>49.3925567626953</v>
+        <v>49.384456062316801</v>
       </c>
       <c r="J5" s="1">
         <f t="shared" ref="J5:J23" si="2">SUM(H5:I5)</f>
-        <v>98.785113525390599</v>
+        <v>98.768912124633601</v>
       </c>
       <c r="L5" s="1">
         <v>1</v>
       </c>
       <c r="M5" s="9">
         <f t="shared" ref="M5:M23" si="3">$J5*B5</f>
-        <v>2.3626066122390323</v>
+        <v>2.3917393330443093</v>
       </c>
       <c r="N5" s="9">
         <f t="shared" ref="N5:N23" si="4">$J5*C5</f>
-        <v>0.93033099468797431</v>
+        <v>0.94735928591224183</v>
       </c>
       <c r="O5" s="9">
         <f t="shared" ref="O5:O23" si="5">$J5*D5</f>
-        <v>0.39854101587086904</v>
+        <v>0.40344906274054587</v>
       </c>
       <c r="P5" s="9">
         <f t="shared" ref="P5:P23" si="6">$J5*E5</f>
-        <v>1.4241359750181433</v>
+        <v>1.4410832790157266</v>
       </c>
       <c r="Q5" s="9">
         <f t="shared" ref="Q5:Q23" si="7">$J5*F5</f>
-        <v>5.1156145978160188</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+        <v>5.183630960712823</v>
+      </c>
+      <c r="T5" s="1">
+        <v>2</v>
+      </c>
+      <c r="U5" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V5" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W5" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X5" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C6" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D6" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B6" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F6" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
       </c>
       <c r="H6" s="1">
-        <v>51.356410331264598</v>
+        <v>51.298140165541703</v>
       </c>
       <c r="I6" s="1">
-        <v>51.356410331264598</v>
+        <v>51.298140165541703</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" si="2"/>
-        <v>102.7128206625292</v>
+        <v>102.59628033108341</v>
       </c>
       <c r="L6" s="1">
         <v>2</v>
       </c>
       <c r="M6" s="9">
         <f t="shared" si="3"/>
-        <v>2.4565441147834512</v>
+        <v>2.4844209965808886</v>
       </c>
       <c r="N6" s="9">
         <f t="shared" si="4"/>
-        <v>0.96732105885182229</v>
+        <v>0.98407015710630852</v>
       </c>
       <c r="O6" s="9">
         <f t="shared" si="5"/>
-        <v>0.41438705113483759</v>
+        <v>0.41908301154527322</v>
       </c>
       <c r="P6" s="9">
         <f t="shared" si="6"/>
-        <v>1.4807597803033079</v>
+        <v>1.4969263191617119</v>
       </c>
       <c r="Q6" s="9">
         <f t="shared" si="7"/>
-        <v>5.3190120050734189</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+        <v>5.3845004843941817</v>
+      </c>
+      <c r="T6" s="1">
+        <v>3</v>
+      </c>
+      <c r="U6" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V6" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W6" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X6" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C7" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D7" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E7" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B7" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D7" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F7" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G7" s="1">
         <v>3</v>
       </c>
       <c r="H7" s="1">
-        <v>53.034496641826998</v>
+        <v>52.920380211466103</v>
       </c>
       <c r="I7" s="1">
-        <v>53.034496641826998</v>
+        <v>52.920380211466103</v>
       </c>
       <c r="J7" s="1">
         <f t="shared" si="2"/>
-        <v>106.068993283654</v>
+        <v>105.84076042293221</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="9">
         <f t="shared" si="3"/>
-        <v>2.5368124400756726</v>
+        <v>2.5629877286024172</v>
       </c>
       <c r="N7" s="9">
         <f t="shared" si="4"/>
-        <v>0.99892856833909993</v>
+        <v>1.0151901550576048</v>
       </c>
       <c r="O7" s="9">
         <f t="shared" si="5"/>
-        <v>0.42792727392880425</v>
+        <v>0.43233599190092392</v>
       </c>
       <c r="P7" s="9">
         <f t="shared" si="6"/>
-        <v>1.5291440560058027</v>
+        <v>1.5442647570252652</v>
       </c>
       <c r="Q7" s="9">
         <f t="shared" si="7"/>
-        <v>5.4928123383493794</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+        <v>5.5547786325862099</v>
+      </c>
+      <c r="T7" s="1">
+        <v>4</v>
+      </c>
+      <c r="U7" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V7" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W7" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X7" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C8" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D8" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B8" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D8" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F8" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G8" s="1">
         <v>4</v>
       </c>
       <c r="H8" s="1">
-        <v>54.659404711418901</v>
+        <v>54.617806617719197</v>
       </c>
       <c r="I8" s="1">
-        <v>54.659404711418901</v>
+        <v>54.617806617719197</v>
       </c>
       <c r="J8" s="1">
         <f t="shared" si="2"/>
-        <v>109.3188094228378</v>
+        <v>109.23561323543839</v>
       </c>
       <c r="L8" s="1">
         <v>4</v>
       </c>
       <c r="M8" s="9">
         <f t="shared" si="3"/>
-        <v>2.6145370771691283</v>
+        <v>2.6451958123699213</v>
       </c>
       <c r="N8" s="9">
         <f t="shared" si="4"/>
-        <v>1.0295344417690353</v>
+        <v>1.0477524792449429</v>
       </c>
       <c r="O8" s="9">
         <f t="shared" si="5"/>
-        <v>0.44103840959775259</v>
+        <v>0.44620321141245811</v>
       </c>
       <c r="P8" s="9">
         <f t="shared" si="6"/>
-        <v>1.5759950430709404</v>
+        <v>1.5937972011676971</v>
       </c>
       <c r="Q8" s="9">
         <f t="shared" si="7"/>
-        <v>5.6611049716068562</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+        <v>5.7329487041950182</v>
+      </c>
+      <c r="T8" s="1">
+        <v>5</v>
+      </c>
+      <c r="U8" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V8" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W8" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X8" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C9" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D9" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B9" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F9" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G9" s="1">
         <v>5</v>
       </c>
       <c r="H9" s="1">
-        <v>56.567297112689999</v>
+        <v>56.617234771834802</v>
       </c>
       <c r="I9" s="1">
-        <v>56.567297112689999</v>
+        <v>56.617234771834802</v>
       </c>
       <c r="J9" s="1">
         <f t="shared" si="2"/>
-        <v>113.13459422538</v>
+        <v>113.2344695436696</v>
       </c>
       <c r="L9" s="1">
         <v>5</v>
       </c>
       <c r="M9" s="9">
         <f t="shared" si="3"/>
-        <v>2.7057977750985813</v>
+        <v>2.742030147322605</v>
       </c>
       <c r="N9" s="9">
         <f t="shared" si="4"/>
-        <v>1.0654704522080161</v>
+        <v>1.0861082085441698</v>
       </c>
       <c r="O9" s="9">
         <f t="shared" si="5"/>
-        <v>0.45643290272812603</v>
+        <v>0.46253765101379929</v>
       </c>
       <c r="P9" s="9">
         <f t="shared" si="6"/>
-        <v>1.6310053195821994</v>
+        <v>1.6521423305916882</v>
       </c>
       <c r="Q9" s="9">
         <f t="shared" si="7"/>
-        <v>5.858706449616923</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+        <v>5.9428183374722616</v>
+      </c>
+      <c r="T9" s="1">
+        <v>6</v>
+      </c>
+      <c r="U9" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V9" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W9" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X9" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C10" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D10" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B10" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F10" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G10" s="1">
         <v>6</v>
       </c>
       <c r="H10" s="1">
-        <v>58.663744490818999</v>
+        <v>58.799297103977402</v>
       </c>
       <c r="I10" s="1">
-        <v>58.663744490818999</v>
+        <v>58.799297103977402</v>
       </c>
       <c r="J10" s="1">
         <f t="shared" si="2"/>
-        <v>117.327488981638</v>
+        <v>117.5985942079548</v>
       </c>
       <c r="L10" s="1">
         <v>6</v>
       </c>
       <c r="M10" s="9">
         <f t="shared" si="3"/>
-        <v>2.8060776707430941</v>
+        <v>2.8477096408935019</v>
       </c>
       <c r="N10" s="9">
         <f t="shared" si="4"/>
-        <v>1.1049579803385463</v>
+        <v>1.1279674731311096</v>
       </c>
       <c r="O10" s="9">
         <f t="shared" si="5"/>
-        <v>0.47334881724159367</v>
+        <v>0.48036413069869233</v>
       </c>
       <c r="P10" s="9">
         <f t="shared" si="6"/>
-        <v>1.691452203214288</v>
+        <v>1.7158168911994383</v>
       </c>
       <c r="Q10" s="9">
         <f t="shared" si="7"/>
-        <v>6.0758366715375223</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+        <v>6.1718581359227409</v>
+      </c>
+      <c r="T10" s="1">
+        <v>7</v>
+      </c>
+      <c r="U10" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V10" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W10" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X10" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C11" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D11" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B11" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F11" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G11" s="1">
         <v>7</v>
       </c>
       <c r="H11" s="1">
-        <v>60.873778125465897</v>
+        <v>61.277551036757799</v>
       </c>
       <c r="I11" s="1">
-        <v>60.873778125465897</v>
+        <v>61.277551036757799</v>
       </c>
       <c r="J11" s="1">
         <f t="shared" si="2"/>
-        <v>121.74755625093179</v>
+        <v>122.5551020735156</v>
       </c>
       <c r="L11" s="1">
         <v>7</v>
       </c>
       <c r="M11" s="9">
         <f t="shared" si="3"/>
-        <v>2.9117907664140397</v>
+        <v>2.9677339943221006</v>
       </c>
       <c r="N11" s="9">
         <f t="shared" si="4"/>
-        <v>1.1465849566356676</v>
+        <v>1.1755086847444445</v>
       </c>
       <c r="O11" s="9">
         <f t="shared" si="5"/>
-        <v>0.49118124195474799</v>
+        <v>0.5006103641522236</v>
       </c>
       <c r="P11" s="9">
         <f t="shared" si="6"/>
-        <v>1.7551741202679498</v>
+        <v>1.7881345917159366</v>
       </c>
       <c r="Q11" s="9">
         <f t="shared" si="7"/>
-        <v>6.3047310852724054</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+        <v>6.4319876349347043</v>
+      </c>
+      <c r="T11" s="1">
+        <v>8</v>
+      </c>
+      <c r="U11" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V11" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W11" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X11" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="B12" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C12" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D12" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B12" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D12" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F12" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G12" s="1">
         <v>8</v>
       </c>
       <c r="H12" s="1">
-        <v>63.477043679766297</v>
+        <v>64.195223213345898</v>
       </c>
       <c r="I12" s="1">
-        <v>63.477043679766297</v>
+        <v>64.195223213345898</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" si="2"/>
-        <v>126.95408735953259</v>
+        <v>128.3904464266918</v>
       </c>
       <c r="L12" s="1">
         <v>8</v>
       </c>
       <c r="M12" s="9">
         <f t="shared" si="3"/>
-        <v>3.0363134235737825</v>
+        <v>3.109039819314261</v>
       </c>
       <c r="N12" s="9">
         <f t="shared" si="4"/>
-        <v>1.1956186327866138</v>
+        <v>1.2314794101534801</v>
       </c>
       <c r="O12" s="9">
         <f t="shared" si="5"/>
-        <v>0.51218659512116116</v>
+        <v>0.52444644940834639</v>
       </c>
       <c r="P12" s="9">
         <f t="shared" si="6"/>
-        <v>1.8302340963331052</v>
+        <v>1.8732749156677657</v>
       </c>
       <c r="Q12" s="9">
         <f t="shared" si="7"/>
-        <v>6.5743527478146628</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+        <v>6.7382405945438517</v>
+      </c>
+      <c r="T12" s="1">
+        <v>9</v>
+      </c>
+      <c r="U12" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V12" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W12" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X12" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C13" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D13" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E13" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B13" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C13" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D13" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F13" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G13" s="1">
         <v>9</v>
       </c>
       <c r="H13" s="1">
-        <v>66.581023953245094</v>
+        <v>67.6095474731151</v>
       </c>
       <c r="I13" s="1">
-        <v>66.581023953245094</v>
+        <v>67.6095474731151</v>
       </c>
       <c r="J13" s="1">
         <f t="shared" si="2"/>
-        <v>133.16204790649019</v>
+        <v>135.2190949462302</v>
       </c>
       <c r="L13" s="1">
         <v>9</v>
       </c>
       <c r="M13" s="9">
         <f t="shared" si="3"/>
-        <v>3.1847868940526234</v>
+        <v>3.2743990088040213</v>
       </c>
       <c r="N13" s="9">
         <f t="shared" si="4"/>
-        <v>1.2540834956037255</v>
+        <v>1.2969775861084032</v>
       </c>
       <c r="O13" s="9">
         <f t="shared" si="5"/>
-        <v>0.53723213907586675</v>
+        <v>0.55233996150368991</v>
       </c>
       <c r="P13" s="9">
         <f t="shared" si="6"/>
-        <v>1.9197311838081654</v>
+        <v>1.9729079984677935</v>
       </c>
       <c r="Q13" s="9">
         <f t="shared" si="7"/>
-        <v>6.895833712540381</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+        <v>7.0966245548839071</v>
+      </c>
+      <c r="T13" s="1">
+        <v>10</v>
+      </c>
+      <c r="U13" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V13" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W13" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X13" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C14" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D14" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B14" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C14" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F14" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G14" s="1">
         <v>10</v>
       </c>
       <c r="H14" s="1">
-        <v>70.346934677467303</v>
+        <v>71.720907692314697</v>
       </c>
       <c r="I14" s="1">
-        <v>70.346934677467303</v>
+        <v>71.720907692314697</v>
       </c>
       <c r="J14" s="1">
         <f t="shared" si="2"/>
-        <v>140.69386935493461</v>
+        <v>143.44181538462939</v>
       </c>
       <c r="L14" s="1">
         <v>10</v>
       </c>
       <c r="M14" s="9">
         <f t="shared" si="3"/>
-        <v>3.36492265055732</v>
+        <v>3.4735163573107051</v>
       </c>
       <c r="N14" s="9">
         <f t="shared" si="4"/>
-        <v>1.3250161158121589</v>
+        <v>1.3758472465633855</v>
       </c>
       <c r="O14" s="9">
         <f t="shared" si="5"/>
-        <v>0.56761869899665385</v>
+        <v>0.58592794766945322</v>
       </c>
       <c r="P14" s="9">
         <f t="shared" si="6"/>
-        <v>2.0283137171408416</v>
+        <v>2.0928812236142371</v>
       </c>
       <c r="Q14" s="9">
         <f t="shared" si="7"/>
-        <v>7.2858711825069751</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+        <v>7.5281727751577794</v>
+      </c>
+      <c r="T14" s="1">
+        <v>11</v>
+      </c>
+      <c r="U14" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V14" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W14" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X14" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C15" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D15" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B15" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F15" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G15" s="1">
         <v>11</v>
       </c>
       <c r="H15" s="1">
-        <v>74.654021112789295</v>
+        <v>76.395587877092495</v>
       </c>
       <c r="I15" s="1">
-        <v>74.654021112789295</v>
+        <v>76.395587877092495</v>
       </c>
       <c r="J15" s="1">
         <f t="shared" si="2"/>
-        <v>149.30804222557859</v>
+        <v>152.79117575418499</v>
       </c>
       <c r="L15" s="1">
         <v>11</v>
       </c>
       <c r="M15" s="9">
         <f t="shared" si="3"/>
-        <v>3.5709446012019637</v>
+        <v>3.699915863528358</v>
       </c>
       <c r="N15" s="9">
         <f t="shared" si="4"/>
-        <v>1.4061420236454332</v>
+        <v>1.4655232708599959</v>
       </c>
       <c r="O15" s="9">
         <f t="shared" si="5"/>
-        <v>0.60237192328556788</v>
+        <v>0.62411800765068548</v>
       </c>
       <c r="P15" s="9">
         <f t="shared" si="6"/>
-        <v>2.1524999739795936</v>
+        <v>2.2292926369652055</v>
       </c>
       <c r="Q15" s="9">
         <f t="shared" si="7"/>
-        <v>7.7319585221125591</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+        <v>8.0188497790042437</v>
+      </c>
+      <c r="T15" s="1">
+        <v>12</v>
+      </c>
+      <c r="U15" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V15" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W15" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X15" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>12</v>
       </c>
-      <c r="B16" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C16" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D16" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E16" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B16" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D16" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F16" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G16" s="1">
         <v>12</v>
       </c>
       <c r="H16" s="1">
-        <v>79.4020157259081</v>
+        <v>81.545743444687503</v>
       </c>
       <c r="I16" s="1">
-        <v>79.4020157259081</v>
+        <v>81.545743444687503</v>
       </c>
       <c r="J16" s="1">
         <f t="shared" si="2"/>
-        <v>158.8040314518162</v>
+        <v>163.09148688937501</v>
       </c>
       <c r="L16" s="1">
         <v>12</v>
       </c>
       <c r="M16" s="9">
         <f t="shared" si="3"/>
-        <v>3.798056623803356</v>
+        <v>3.9493431251503268</v>
       </c>
       <c r="N16" s="9">
         <f t="shared" si="4"/>
-        <v>1.4955726350717311</v>
+        <v>1.56432050565584</v>
       </c>
       <c r="O16" s="9">
         <f t="shared" si="5"/>
-        <v>0.64068276849151917</v>
+        <v>0.66619249023873428</v>
       </c>
       <c r="P16" s="9">
         <f t="shared" si="6"/>
-        <v>2.2893989397533558</v>
+        <v>2.3795788538150084</v>
       </c>
       <c r="Q16" s="9">
         <f t="shared" si="7"/>
-        <v>8.2237109671199615</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+        <v>8.5594349748599079</v>
+      </c>
+      <c r="T16" s="1">
+        <v>13</v>
+      </c>
+      <c r="U16" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V16" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W16" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X16" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>13</v>
       </c>
-      <c r="B17" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C17" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D17" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B17" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D17" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F17" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G17" s="1">
         <v>13</v>
       </c>
       <c r="H17" s="1">
-        <v>84.472264090920007</v>
+        <v>87.063869838910094</v>
       </c>
       <c r="I17" s="1">
-        <v>84.472264090920007</v>
+        <v>87.063869838910094</v>
       </c>
       <c r="J17" s="1">
         <f t="shared" si="2"/>
-        <v>168.94452818184001</v>
+        <v>174.12773967782019</v>
       </c>
       <c r="L17" s="1">
         <v>13</v>
       </c>
       <c r="M17" s="9">
         <f t="shared" si="3"/>
-        <v>4.0405830913118903</v>
+        <v>4.2165915874016484</v>
       </c>
       <c r="N17" s="9">
         <f t="shared" si="4"/>
-        <v>1.591073040677363</v>
+        <v>1.6701766534649318</v>
       </c>
       <c r="O17" s="9">
         <f t="shared" si="5"/>
-        <v>0.68159383012815089</v>
+        <v>0.7112731309776682</v>
       </c>
       <c r="P17" s="9">
         <f t="shared" si="6"/>
-        <v>2.4355894504730595</v>
+        <v>2.5406027935780591</v>
       </c>
       <c r="Q17" s="9">
         <f t="shared" si="7"/>
-        <v>8.7488394125904652</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+        <v>9.1386441654223063</v>
+      </c>
+      <c r="T17" s="1">
+        <v>14</v>
+      </c>
+      <c r="U17" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V17" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W17" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X17" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>14</v>
       </c>
-      <c r="B18" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C18" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D18" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B18" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C18" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D18" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F18" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G18" s="1">
         <v>14</v>
       </c>
       <c r="H18" s="1">
-        <v>89.874542418862802</v>
+        <v>92.979264470914401</v>
       </c>
       <c r="I18" s="1">
-        <v>89.874542418862802</v>
+        <v>92.979264470914401</v>
       </c>
       <c r="J18" s="1">
         <f t="shared" si="2"/>
-        <v>179.7490848377256</v>
+        <v>185.9585289418288</v>
       </c>
       <c r="L18" s="1">
         <v>14</v>
       </c>
       <c r="M18" s="9">
         <f t="shared" si="3"/>
-        <v>4.2989916316932852</v>
+        <v>4.5030801536418199</v>
       </c>
       <c r="N18" s="9">
         <f t="shared" si="4"/>
-        <v>1.6928273797888833</v>
+        <v>1.7836537367680907</v>
       </c>
       <c r="O18" s="9">
         <f t="shared" si="5"/>
-        <v>0.72518399095298225</v>
+        <v>0.75959927669872385</v>
       </c>
       <c r="P18" s="9">
         <f t="shared" si="6"/>
-        <v>2.5913533837079337</v>
+        <v>2.7132193813198349</v>
       </c>
       <c r="Q18" s="9">
         <f t="shared" si="7"/>
-        <v>9.3083563861430854</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+        <v>9.7595525484284682</v>
+      </c>
+      <c r="T18" s="1">
+        <v>15</v>
+      </c>
+      <c r="U18" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V18" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W18" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X18" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>15</v>
       </c>
-      <c r="B19" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C19" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D19" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E19" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B19" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C19" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D19" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F19" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G19" s="1">
         <v>15</v>
       </c>
       <c r="H19" s="1">
-        <v>95.451611366954793</v>
+        <v>99.093713264115607</v>
       </c>
       <c r="I19" s="1">
-        <v>95.451611366954793</v>
+        <v>99.093713264115607</v>
       </c>
       <c r="J19" s="1">
         <f t="shared" si="2"/>
-        <v>190.90322273390959</v>
+        <v>198.18742652823121</v>
       </c>
       <c r="L19" s="1">
         <v>15</v>
       </c>
       <c r="M19" s="9">
         <f t="shared" si="3"/>
-        <v>4.5657609758473194</v>
+        <v>4.7992091149516467</v>
       </c>
       <c r="N19" s="9">
         <f t="shared" si="4"/>
-        <v>1.7978739787501374</v>
+        <v>1.9009493456366904</v>
       </c>
       <c r="O19" s="9">
         <f t="shared" si="5"/>
-        <v>0.77018451066353899</v>
+        <v>0.80955160646984092</v>
       </c>
       <c r="P19" s="9">
         <f t="shared" si="6"/>
-        <v>2.7521570562591213</v>
+        <v>2.8916445502669479</v>
       </c>
       <c r="Q19" s="9">
         <f t="shared" si="7"/>
-        <v>9.8859765215201172</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+        <v>10.401354617325124</v>
+      </c>
+      <c r="T19" s="1">
+        <v>16</v>
+      </c>
+      <c r="U19" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V19" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W19" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X19" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>16</v>
       </c>
-      <c r="B20" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C20" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D20" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B20" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C20" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D20" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F20" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G20" s="1">
         <v>16</v>
       </c>
       <c r="H20" s="1">
-        <v>101.329487642438</v>
+        <v>105.566110241906</v>
       </c>
       <c r="I20" s="1">
-        <v>101.329487642438</v>
+        <v>105.566110241906</v>
       </c>
       <c r="J20" s="1">
         <f t="shared" si="2"/>
-        <v>202.65897528487599</v>
+        <v>211.13222048381201</v>
       </c>
       <c r="L20" s="1">
         <v>16</v>
       </c>
       <c r="M20" s="9">
         <f t="shared" si="3"/>
-        <v>4.8469189126818035</v>
+        <v>5.1126738701637784</v>
       </c>
       <c r="N20" s="9">
         <f t="shared" si="4"/>
-        <v>1.9085864188510966</v>
+        <v>2.0251115996723059</v>
       </c>
       <c r="O20" s="9">
         <f t="shared" si="5"/>
-        <v>0.81761219887269909</v>
+        <v>0.86242821385980939</v>
       </c>
       <c r="P20" s="9">
         <f t="shared" si="6"/>
-        <v>2.921633908831037</v>
+        <v>3.0805149723300329</v>
       </c>
       <c r="Q20" s="9">
         <f t="shared" si="7"/>
-        <v>10.494751439236635</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+        <v>11.080728656025924</v>
+      </c>
+      <c r="T20" s="1">
+        <v>17</v>
+      </c>
+      <c r="U20" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V20" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W20" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X20" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>17</v>
       </c>
-      <c r="B21" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C21" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D21" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B21" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C21" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D21" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F21" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G21" s="1">
         <v>17</v>
       </c>
       <c r="H21" s="1">
-        <v>107.51541953840599</v>
+        <v>112.407162426556</v>
       </c>
       <c r="I21" s="1">
-        <v>107.51541953840599</v>
+        <v>112.407162426556</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" si="2"/>
-        <v>215.03083907681199</v>
+        <f>SUM(H21:I21)</f>
+        <v>224.814324853112</v>
       </c>
       <c r="L21" s="1">
         <v>17</v>
       </c>
       <c r="M21" s="9">
         <f t="shared" si="3"/>
-        <v>5.1428121516265124</v>
+        <v>5.4439929712345556</v>
       </c>
       <c r="N21" s="9">
         <f t="shared" si="4"/>
-        <v>2.0251012249482478</v>
+        <v>2.1563458954264254</v>
       </c>
       <c r="O21" s="9">
         <f t="shared" si="5"/>
-        <v>0.86752554095320256</v>
+        <v>0.91831657048306392</v>
       </c>
       <c r="P21" s="9">
         <f t="shared" si="6"/>
-        <v>3.0999929315150752</v>
+        <v>3.2801430881430922</v>
       </c>
       <c r="Q21" s="9">
         <f t="shared" si="7"/>
-        <v>11.135431849043039</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+        <v>11.798798525287134</v>
+      </c>
+      <c r="T21" s="1">
+        <v>18</v>
+      </c>
+      <c r="U21" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V21" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W21" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X21" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>18</v>
       </c>
-      <c r="B22" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C22" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D22" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B22" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C22" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D22" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F22" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G22" s="1">
         <v>18</v>
       </c>
       <c r="H22" s="1">
-        <v>114.11017852237499</v>
+        <v>119.72821179112501</v>
       </c>
       <c r="I22" s="1">
-        <v>114.11017852237499</v>
+        <v>119.72821179112501</v>
       </c>
       <c r="J22" s="1">
         <f t="shared" si="2"/>
-        <v>228.22035704474999</v>
+        <v>239.45642358225001</v>
       </c>
       <c r="L22" s="1">
         <v>18</v>
       </c>
       <c r="M22" s="9">
         <f t="shared" si="3"/>
-        <v>5.4582609196768361</v>
+        <v>5.7985588229329785</v>
       </c>
       <c r="N22" s="9">
         <f t="shared" si="4"/>
-        <v>2.1493164729006913</v>
+        <v>2.2967881448944452</v>
       </c>
       <c r="O22" s="9">
         <f t="shared" si="5"/>
-        <v>0.92073764652453449</v>
+        <v>0.9781262907862599</v>
       </c>
       <c r="P22" s="9">
         <f t="shared" si="6"/>
-        <v>3.290139668821408</v>
+        <v>3.493777957601127</v>
       </c>
       <c r="Q22" s="9">
         <f t="shared" si="7"/>
-        <v>11.81845470792347</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+        <v>12.567251216214808</v>
+      </c>
+      <c r="T22" s="1">
+        <v>19</v>
+      </c>
+      <c r="U22" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="V22" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="W22" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="X22" s="1">
+        <v>1.4590454101562501E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
-      <c r="B23" s="3">
-        <v>2.3916625976562501E-2</v>
-      </c>
-      <c r="C23" s="3">
-        <v>9.4177246093750007E-3</v>
-      </c>
-      <c r="D23" s="3">
-        <v>4.0344238281249997E-3</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1.4416503906249999E-2</v>
+      <c r="B23" s="1">
+        <v>2.4215507507324201E-2</v>
+      </c>
+      <c r="C23" s="1">
+        <v>9.5916748046875003E-3</v>
+      </c>
+      <c r="D23" s="1">
+        <v>4.0847778320312498E-3</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1.4590454101562501E-2</v>
       </c>
       <c r="F23" s="3">
         <f t="shared" si="1"/>
-        <v>5.1785278320312503E-2</v>
+        <v>5.2482414245605444E-2</v>
       </c>
       <c r="G23" s="1">
         <v>19</v>
       </c>
       <c r="H23" s="1">
-        <v>121.042317395501</v>
+        <v>127.44447616031501</v>
       </c>
       <c r="I23" s="1">
-        <v>121.042317395501</v>
+        <v>127.44447616031501</v>
       </c>
       <c r="J23" s="1">
         <f t="shared" si="2"/>
-        <v>242.084634791002</v>
+        <v>254.88895232063001</v>
       </c>
       <c r="L23" s="1">
         <v>19</v>
       </c>
       <c r="M23" s="9">
         <f t="shared" si="3"/>
-        <v>5.7898476649691251</v>
+        <v>6.1722653384542161</v>
       </c>
       <c r="N23" s="9">
         <f t="shared" si="4"/>
-        <v>2.2798864226227789</v>
+        <v>2.4448119419669805</v>
       </c>
       <c r="O23" s="9">
         <f t="shared" si="5"/>
-        <v>0.97667201902375678</v>
+        <v>1.0411647420689796</v>
       </c>
       <c r="P23" s="9">
         <f t="shared" si="6"/>
-        <v>3.4900140831075848</v>
+        <v>3.7189455598295047</v>
       </c>
       <c r="Q23" s="9">
         <f t="shared" si="7"/>
-        <v>12.536420189723247</v>
+        <v>13.37718758231968</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="P30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="O31" s="1">
+        <v>0</v>
+      </c>
+      <c r="P31" s="1">
+        <v>50</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="O32" s="1">
+        <v>1</v>
+      </c>
+      <c r="P32" s="1">
+        <v>49.384456062316801</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>49.384456062316801</v>
+      </c>
+    </row>
+    <row r="33" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O33" s="1">
+        <v>2</v>
+      </c>
+      <c r="P33" s="1">
+        <v>51.298140165541703</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>51.298140165541703</v>
+      </c>
+    </row>
+    <row r="34" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O34" s="1">
+        <v>3</v>
+      </c>
+      <c r="P34" s="1">
+        <v>52.920380211466103</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>52.920380211466103</v>
+      </c>
+    </row>
+    <row r="35" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O35" s="1">
+        <v>4</v>
+      </c>
+      <c r="P35" s="1">
+        <v>54.617806617719197</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>54.617806617719197</v>
+      </c>
+    </row>
+    <row r="36" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O36" s="1">
+        <v>5</v>
+      </c>
+      <c r="P36" s="1">
+        <v>56.617234771834802</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>56.617234771834802</v>
+      </c>
+    </row>
+    <row r="37" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O37" s="1">
+        <v>6</v>
+      </c>
+      <c r="P37" s="1">
+        <v>58.799297103977402</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>58.799297103977402</v>
+      </c>
+    </row>
+    <row r="38" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O38" s="1">
+        <v>7</v>
+      </c>
+      <c r="P38" s="1">
+        <v>61.277551036757799</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>61.277551036757799</v>
+      </c>
+    </row>
+    <row r="39" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O39" s="1">
+        <v>8</v>
+      </c>
+      <c r="P39" s="1">
+        <v>64.195223213345898</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>64.195223213345898</v>
+      </c>
+    </row>
+    <row r="40" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O40" s="1">
+        <v>9</v>
+      </c>
+      <c r="P40" s="1">
+        <v>67.6095474731151</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>67.6095474731151</v>
+      </c>
+    </row>
+    <row r="41" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O41" s="1">
+        <v>10</v>
+      </c>
+      <c r="P41" s="1">
+        <v>71.720907692314697</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>71.720907692314697</v>
+      </c>
+    </row>
+    <row r="42" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O42" s="1">
+        <v>11</v>
+      </c>
+      <c r="P42" s="1">
+        <v>76.395587877092495</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>76.395587877092495</v>
+      </c>
+    </row>
+    <row r="43" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O43" s="1">
+        <v>12</v>
+      </c>
+      <c r="P43" s="1">
+        <v>81.545743444687503</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>81.545743444687503</v>
+      </c>
+    </row>
+    <row r="44" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O44" s="1">
+        <v>13</v>
+      </c>
+      <c r="P44" s="1">
+        <v>87.063869838910094</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>87.063869838910094</v>
+      </c>
+    </row>
+    <row r="45" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O45" s="1">
+        <v>14</v>
+      </c>
+      <c r="P45" s="1">
+        <v>92.979264470914401</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>92.979264470914401</v>
+      </c>
+    </row>
+    <row r="46" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O46" s="1">
+        <v>15</v>
+      </c>
+      <c r="P46" s="1">
+        <v>99.093713264115607</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>99.093713264115607</v>
+      </c>
+    </row>
+    <row r="47" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O47" s="1">
+        <v>16</v>
+      </c>
+      <c r="P47" s="1">
+        <v>105.566110241906</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>105.566110241906</v>
+      </c>
+    </row>
+    <row r="48" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O48" s="1">
+        <v>17</v>
+      </c>
+      <c r="P48" s="1">
+        <v>112.407162426556</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>112.407162426556</v>
+      </c>
+    </row>
+    <row r="49" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O49" s="1">
+        <v>18</v>
+      </c>
+      <c r="P49" s="1">
+        <v>119.72821179112501</v>
+      </c>
+      <c r="Q49" s="1">
+        <v>119.72821179112501</v>
+      </c>
+    </row>
+    <row r="50" spans="15:17" x14ac:dyDescent="0.2">
+      <c r="O50" s="1">
+        <v>19</v>
+      </c>
+      <c r="P50" s="1">
+        <v>127.44447616031501</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>127.44447616031501</v>
       </c>
     </row>
   </sheetData>
